--- a/multi seed generators/merged 10 seeds/classification/results/aggregated/compute_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/classification/results/aggregated/compute_mean_sd.xlsx
@@ -333,12 +333,10 @@
       <c r="O3" t="n">
         <v>0.0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P3"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -617,12 +615,10 @@
       <c r="O7" t="n">
         <v>0.0</v>
       </c>
-      <c r="P7" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P7"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -901,12 +897,10 @@
       <c r="O11" t="n">
         <v>0.0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P11"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1185,12 +1179,10 @@
       <c r="O15" t="n">
         <v>0.0</v>
       </c>
-      <c r="P15" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P15"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -1469,12 +1461,10 @@
       <c r="O19" t="n">
         <v>0.0</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P19"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -1753,12 +1743,10 @@
       <c r="O23" t="n">
         <v>0.0</v>
       </c>
-      <c r="P23" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P23"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -2037,12 +2025,10 @@
       <c r="O27" t="n">
         <v>0.0</v>
       </c>
-      <c r="P27" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P27"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -2321,12 +2307,10 @@
       <c r="O31" t="n">
         <v>0.0</v>
       </c>
-      <c r="P31" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P31"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -2605,12 +2589,10 @@
       <c r="O35" t="n">
         <v>0.0</v>
       </c>
-      <c r="P35" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P35"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -2889,12 +2871,10 @@
       <c r="O39" t="n">
         <v>0.0</v>
       </c>
-      <c r="P39" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P39"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3173,12 +3153,10 @@
       <c r="O43" t="n">
         <v>0.0</v>
       </c>
-      <c r="P43" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P43"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -3457,12 +3435,10 @@
       <c r="O47" t="n">
         <v>0.0</v>
       </c>
-      <c r="P47" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P47"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -3741,12 +3717,10 @@
       <c r="O51" t="n">
         <v>0.0</v>
       </c>
-      <c r="P51" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P51"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -4025,12 +3999,10 @@
       <c r="O55" t="n">
         <v>0.0</v>
       </c>
-      <c r="P55" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P55"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -4309,12 +4281,10 @@
       <c r="O59" t="n">
         <v>0.0</v>
       </c>
-      <c r="P59" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P59"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -4593,12 +4563,10 @@
       <c r="O63" t="n">
         <v>0.0</v>
       </c>
-      <c r="P63" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P63"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -4877,12 +4845,10 @@
       <c r="O67" t="n">
         <v>0.0</v>
       </c>
-      <c r="P67" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P67"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -5161,12 +5127,10 @@
       <c r="O71" t="n">
         <v>0.0</v>
       </c>
-      <c r="P71" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P71"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -5445,12 +5409,10 @@
       <c r="O75" t="n">
         <v>0.0</v>
       </c>
-      <c r="P75" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P75"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -5729,12 +5691,10 @@
       <c r="O79" t="n">
         <v>0.0</v>
       </c>
-      <c r="P79" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P79"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -6013,12 +5973,10 @@
       <c r="O83" t="n">
         <v>0.0</v>
       </c>
-      <c r="P83" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P83"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -6297,12 +6255,10 @@
       <c r="O87" t="n">
         <v>0.0</v>
       </c>
-      <c r="P87" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P87"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -6581,12 +6537,10 @@
       <c r="O91" t="n">
         <v>0.0</v>
       </c>
-      <c r="P91" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P91"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -6865,12 +6819,10 @@
       <c r="O95" t="n">
         <v>0.0</v>
       </c>
-      <c r="P95" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P95"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -7149,12 +7101,10 @@
       <c r="O99" t="n">
         <v>0.0</v>
       </c>
-      <c r="P99" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P99"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -7433,12 +7383,10 @@
       <c r="O103" t="n">
         <v>0.0</v>
       </c>
-      <c r="P103" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P103"/>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -7717,12 +7665,10 @@
       <c r="O107" t="n">
         <v>0.0</v>
       </c>
-      <c r="P107" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P107"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -8001,12 +7947,10 @@
       <c r="O111" t="n">
         <v>0.0</v>
       </c>
-      <c r="P111" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P111"/>
       <c r="Q111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -8285,12 +8229,10 @@
       <c r="O115" t="n">
         <v>0.0</v>
       </c>
-      <c r="P115" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P115"/>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -8569,12 +8511,10 @@
       <c r="O119" t="n">
         <v>0.0</v>
       </c>
-      <c r="P119" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P119"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -8853,12 +8793,10 @@
       <c r="O123" t="n">
         <v>0.0</v>
       </c>
-      <c r="P123" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P123"/>
       <c r="Q123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -9137,12 +9075,10 @@
       <c r="O127" t="n">
         <v>0.0</v>
       </c>
-      <c r="P127" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P127"/>
       <c r="Q127" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R127" t="n">
@@ -9421,12 +9357,10 @@
       <c r="O131" t="n">
         <v>0.0</v>
       </c>
-      <c r="P131" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P131"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R131" t="n">
@@ -9705,12 +9639,10 @@
       <c r="O135" t="n">
         <v>0.0</v>
       </c>
-      <c r="P135" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P135"/>
       <c r="Q135" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -9989,12 +9921,10 @@
       <c r="O139" t="n">
         <v>0.0</v>
       </c>
-      <c r="P139" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P139"/>
       <c r="Q139" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R139" t="n">
@@ -10273,12 +10203,10 @@
       <c r="O143" t="n">
         <v>0.0</v>
       </c>
-      <c r="P143" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P143"/>
       <c r="Q143" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -10557,12 +10485,10 @@
       <c r="O147" t="n">
         <v>0.0</v>
       </c>
-      <c r="P147" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P147"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R147" t="n">
@@ -10841,12 +10767,10 @@
       <c r="O151" t="n">
         <v>0.0</v>
       </c>
-      <c r="P151" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P151"/>
       <c r="Q151" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R151" t="n">
@@ -11125,12 +11049,10 @@
       <c r="O155" t="n">
         <v>0.0</v>
       </c>
-      <c r="P155" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P155"/>
       <c r="Q155" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R155" t="n">
@@ -11409,12 +11331,10 @@
       <c r="O159" t="n">
         <v>0.0</v>
       </c>
-      <c r="P159" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P159"/>
       <c r="Q159" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R159" t="n">
@@ -11693,12 +11613,10 @@
       <c r="O163" t="n">
         <v>0.0</v>
       </c>
-      <c r="P163" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P163"/>
       <c r="Q163" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R163" t="n">
@@ -11977,12 +11895,10 @@
       <c r="O167" t="n">
         <v>0.0</v>
       </c>
-      <c r="P167" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P167"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R167" t="n">
@@ -12261,12 +12177,10 @@
       <c r="O171" t="n">
         <v>0.0</v>
       </c>
-      <c r="P171" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P171"/>
       <c r="Q171" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R171" t="n">
@@ -12545,12 +12459,10 @@
       <c r="O175" t="n">
         <v>0.0</v>
       </c>
-      <c r="P175" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P175"/>
       <c r="Q175" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R175" t="n">
@@ -12829,12 +12741,10 @@
       <c r="O179" t="n">
         <v>0.0</v>
       </c>
-      <c r="P179" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P179"/>
       <c r="Q179" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R179" t="n">
@@ -13113,12 +13023,10 @@
       <c r="O183" t="n">
         <v>0.0</v>
       </c>
-      <c r="P183" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P183"/>
       <c r="Q183" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R183" t="n">
@@ -13397,12 +13305,10 @@
       <c r="O187" t="n">
         <v>0.0</v>
       </c>
-      <c r="P187" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P187"/>
       <c r="Q187" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R187" t="n">
@@ -13681,12 +13587,10 @@
       <c r="O191" t="n">
         <v>0.0</v>
       </c>
-      <c r="P191" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P191"/>
       <c r="Q191" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R191" t="n">
@@ -13965,12 +13869,10 @@
       <c r="O195" t="n">
         <v>0.0</v>
       </c>
-      <c r="P195" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P195"/>
       <c r="Q195" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R195" t="n">
@@ -14249,12 +14151,10 @@
       <c r="O199" t="n">
         <v>0.0</v>
       </c>
-      <c r="P199" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P199"/>
       <c r="Q199" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R199" t="n">
@@ -14533,12 +14433,10 @@
       <c r="O203" t="n">
         <v>0.0</v>
       </c>
-      <c r="P203" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P203"/>
       <c r="Q203" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R203" t="n">
@@ -14817,12 +14715,10 @@
       <c r="O207" t="n">
         <v>0.0</v>
       </c>
-      <c r="P207" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P207"/>
       <c r="Q207" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R207" t="n">
@@ -15101,12 +14997,10 @@
       <c r="O211" t="n">
         <v>0.0</v>
       </c>
-      <c r="P211" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P211"/>
       <c r="Q211" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R211" t="n">
@@ -15385,12 +15279,10 @@
       <c r="O215" t="n">
         <v>0.0</v>
       </c>
-      <c r="P215" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P215"/>
       <c r="Q215" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R215" t="n">
@@ -15669,12 +15561,10 @@
       <c r="O219" t="n">
         <v>0.0</v>
       </c>
-      <c r="P219" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P219"/>
       <c r="Q219" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R219" t="n">
@@ -15953,12 +15843,10 @@
       <c r="O223" t="n">
         <v>0.0</v>
       </c>
-      <c r="P223" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P223"/>
       <c r="Q223" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R223" t="n">
@@ -16237,12 +16125,10 @@
       <c r="O227" t="n">
         <v>0.0</v>
       </c>
-      <c r="P227" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P227"/>
       <c r="Q227" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R227" t="n">
@@ -16521,12 +16407,10 @@
       <c r="O231" t="n">
         <v>0.0</v>
       </c>
-      <c r="P231" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P231"/>
       <c r="Q231" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R231" t="n">
@@ -16805,12 +16689,10 @@
       <c r="O235" t="n">
         <v>0.0</v>
       </c>
-      <c r="P235" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P235"/>
       <c r="Q235" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R235" t="n">
@@ -17089,12 +16971,10 @@
       <c r="O239" t="n">
         <v>0.0</v>
       </c>
-      <c r="P239" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P239"/>
       <c r="Q239" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R239" t="n">
@@ -17373,12 +17253,10 @@
       <c r="O243" t="n">
         <v>0.0</v>
       </c>
-      <c r="P243" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P243"/>
       <c r="Q243" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R243" t="n">
@@ -17657,12 +17535,10 @@
       <c r="O247" t="n">
         <v>0.0</v>
       </c>
-      <c r="P247" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P247"/>
       <c r="Q247" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R247" t="n">
@@ -17941,12 +17817,10 @@
       <c r="O251" t="n">
         <v>0.0</v>
       </c>
-      <c r="P251" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P251"/>
       <c r="Q251" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R251" t="n">
@@ -18225,12 +18099,10 @@
       <c r="O255" t="n">
         <v>0.0</v>
       </c>
-      <c r="P255" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P255"/>
       <c r="Q255" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R255" t="n">
@@ -18509,12 +18381,10 @@
       <c r="O259" t="n">
         <v>0.0</v>
       </c>
-      <c r="P259" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P259"/>
       <c r="Q259" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R259" t="n">
@@ -18793,12 +18663,10 @@
       <c r="O263" t="n">
         <v>0.0</v>
       </c>
-      <c r="P263" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P263"/>
       <c r="Q263" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R263" t="n">
@@ -19077,12 +18945,10 @@
       <c r="O267" t="n">
         <v>0.0</v>
       </c>
-      <c r="P267" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P267"/>
       <c r="Q267" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R267" t="n">
@@ -19361,12 +19227,10 @@
       <c r="O271" t="n">
         <v>0.0</v>
       </c>
-      <c r="P271" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P271"/>
       <c r="Q271" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R271" t="n">
@@ -19645,12 +19509,10 @@
       <c r="O275" t="n">
         <v>0.0</v>
       </c>
-      <c r="P275" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P275"/>
       <c r="Q275" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R275" t="n">
@@ -19929,12 +19791,10 @@
       <c r="O279" t="n">
         <v>0.0</v>
       </c>
-      <c r="P279" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P279"/>
       <c r="Q279" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R279" t="n">
@@ -20213,12 +20073,10 @@
       <c r="O283" t="n">
         <v>0.0</v>
       </c>
-      <c r="P283" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P283"/>
       <c r="Q283" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R283" t="n">
@@ -20497,12 +20355,10 @@
       <c r="O287" t="n">
         <v>0.0</v>
       </c>
-      <c r="P287" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P287"/>
       <c r="Q287" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R287" t="n">
